--- a/results/run_1/metrics_all_models.xlsx
+++ b/results/run_1/metrics_all_models.xlsx
@@ -486,12 +486,12 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Train Time (s)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -507,43 +507,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1032112804944665</v>
+        <v>0.001855810355352211</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3212651249271644</v>
+        <v>0.04307911739291105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.293421082839479</v>
+        <v>0.01795608702838828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7856229770131442</v>
+        <v>0.3203747300000011</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2925793702461091</v>
+        <v>-0.00034129841346154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8008530208785685</v>
+        <v>0.9963948217263092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.410323091839259</v>
+        <v>0.1891187568251931</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01760859260085675</v>
+        <v>0.00185569387074518</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1326973722454848</v>
+        <v>0.04307776538709013</v>
       </c>
       <c r="K2" t="n">
-        <v>1.937163798433682e-05</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0819668999993155</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>RC basé IDF, sans airgap</t>
-        </is>
-      </c>
+        <v>3.498224249266557e-05</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -553,44 +551,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009072709912407451</v>
+        <v>0.001822442056239015</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0301209394149775</v>
+        <v>0.04269006976146812</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01262911213950579</v>
+        <v>0.01841747201148197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2320559151564154</v>
+        <v>0.4377121639128774</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001800999409642043</v>
+        <v>0.0003876900003596321</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9982501115139931</v>
+        <v>0.9960812006324775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1322374838452074</v>
+        <v>0.1880176457251871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009072385552520099</v>
+        <v>0.001822291752702637</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03012040098093002</v>
+        <v>0.04268830932120218</v>
       </c>
       <c r="K3" t="n">
-        <v>7.139420893835605e-05</v>
-      </c>
-      <c r="L3" t="n">
-        <v>103.5603257999992</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>3.357124756939468e-05</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>PySR pour l'année airport</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>96.75228590000188</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.008501899999828311</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,45 +599,45 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009070434399469005</v>
+        <v>0.001817840417831737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03011716188399731</v>
+        <v>0.04263613980922449</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01271243468082023</v>
+        <v>0.01843914040810124</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2320686956743607</v>
+        <v>0.4368421583624844</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0001880098207100952</v>
+        <v>0.0004931878297723691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9982505504009331</v>
+        <v>0.996091095541135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1322208996615243</v>
+        <v>0.1877801248517948</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009070080922542169</v>
+        <v>0.001817597183596302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03011657504189706</v>
+        <v>0.04263328727175869</v>
       </c>
       <c r="K4" t="n">
-        <v>7.138643098826362e-05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.004124400000364403</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>3.357123585351209e-05</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>rl en utilisant train_test_split</t>
         </is>
       </c>
+      <c r="M4" t="n">
+        <v>0.00256470000022091</v>
+      </c>
       <c r="N4" t="n">
-        <v>0.0003113000002485933</v>
+        <v>0.00036040000122739</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +647,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1032112804944665</v>
+        <v>0.2322888711374143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3212651249271644</v>
+        <v>0.4819635578935552</v>
       </c>
       <c r="D5" t="n">
-        <v>0.293421082839479</v>
+        <v>0.4402194931285253</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7856229770131442</v>
+        <v>1.177553377988573</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2925793702461091</v>
+        <v>-0.4389499083256129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8008530208785685</v>
+        <v>0.5479386233250889</v>
       </c>
       <c r="H5" t="n">
-        <v>1.410323091839259</v>
+        <v>2.115438827342663</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01760859260085675</v>
+        <v>0.03961184911835037</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1326973722454848</v>
+        <v>0.1990272572246082</v>
       </c>
       <c r="K5" t="n">
-        <v>1.937163798433682e-05</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0819668999993155</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>RC basé IDF, sans airgap</t>
-        </is>
+        <v>3.576850390521867e-05</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06975969999984954</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
